--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -701,37 +715,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA 1</t>
+          <t>SOUTH AFRICA 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Al-Ettifaq x Al Nassr</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Al-Ettifaq</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Al Nassr</t>
-        </is>
-      </c>
+          <t>Orlando Pirates x Sekhukhune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Match Odds (Away)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -740,37 +746,45 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="L4" t="n">
-        <v>15.15</v>
+        <v>7.14</v>
       </c>
       <c r="M4" t="n">
         <v>100</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>LIQUIDADO</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,37 +794,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ENGLAND CUP</t>
+          <t>SAUDI ARABIA 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doncaster x Middlesbrough</t>
+          <t>Al-Ettifaq x Al Nassr</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -819,20 +833,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="L5" t="n">
-        <v>19.23</v>
+        <v>15.15</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,6 +864,8 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,7 +875,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -869,27 +885,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cambridge Utd x Millwall</t>
+          <t>Doncaster x Middlesbrough</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cambridge Utd</t>
+          <t>Doncaster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +914,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="L6" t="n">
-        <v>3.57</v>
+        <v>19.23</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +945,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -963,12 +981,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,13 +995,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6.06</v>
+        <v>3.57</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
@@ -1008,6 +1026,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1027,17 +1047,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Walsall x Leyton Orient</t>
+          <t>Cambridge Utd x Millwall</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cambridge Utd</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1069,7 +1089,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1087,6 +1107,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1106,27 +1128,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sheff Wed x Wolves</t>
+          <t>Walsall x Leyton Orient</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sheff Wed</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wolves</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,20 +1157,20 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>17.86</v>
+        <v>6.06</v>
       </c>
       <c r="M9" t="n">
         <v>100</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1166,6 +1188,8 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1199,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EUROPA CHAMPIONS LEAGUE</t>
+          <t>ENGLAND CUP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bodo Glimt x NEC Nijmegen</t>
+          <t>Sheff Wed x Wolves</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Sheff Wed</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NEC Nijmegen</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1238,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17</v>
+        <v>6.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="L10" t="n">
-        <v>6.25</v>
+        <v>17.86</v>
       </c>
       <c r="M10" t="n">
         <v>100</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1245,6 +1269,8 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1280,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICELAND 2</t>
+          <t>EUROPA CHAMPIONS LEAGUE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Afturelding x Grotta</t>
+          <t>Bodo Glimt x NEC Nijmegen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grotta</t>
+          <t>NEC Nijmegen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1319,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1350,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1333,37 +1361,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PARAGUAY CUP</t>
+          <t>ICELAND 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sol de America x Sportivo Trinidense</t>
+          <t>Afturelding x Grotta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sol de America</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Grotta</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1372,20 +1400,20 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>12.5</v>
       </c>
       <c r="M12" t="n">
         <v>100</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1403,6 +1431,8 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1412,37 +1442,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARGENTINA 2</t>
+          <t>PARAGUAY CUP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Madryn x Godoy Cruz</t>
+          <t>Sol de America x Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Sol de America</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lay Over 4.5 FT (Under Pesado)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Over 4.5 FT</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1451,20 +1481,20 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5.71</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
         <v>100</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1482,6 +1512,8 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1491,29 +1523,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SOUTH AFRICA 1</t>
+          <t>ARGENTINA 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Orlando Pirates x Sekhukhune</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>Deportivo Madryn x Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lay Away Fortaleza 1X (Fav &lt;= 1.40 | O25 &gt;= 1.75)</t>
+          <t>Lay Over 4.5 FT (Under Pesado)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Match Odds (Away)</t>
+          <t>Over 4.5 FT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1522,13 +1562,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="K14" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="L14" t="n">
-        <v>7.14</v>
+        <v>5.71</v>
       </c>
       <c r="M14" t="n">
         <v>100</v>
@@ -1540,24 +1580,107 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>LIQUIDADO</t>
-        </is>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>COLOMBIA 1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga x Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aguilas Doradas</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Correct Score (3x0)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>32</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>200</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>vs</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2x1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1x3</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2x1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-25.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1656,19 +1656,19 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S15" t="n">
